--- a/education_forms/043_ged_practice_test_booking_form--education_forms.xlsx
+++ b/education_forms/043_ged_practice_test_booking_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -905,7 +905,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Assigned Teachers Comments</t>
+          <t>Assigned Teachers Comments 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_teacher</t>
+          <t>assigned_teacher_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Assigned Teacher</t>
+          <t>Assigned Teacher 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -969,12 +969,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>assigned_teachers_comments_2</t>
+          <t>assigned_teachers_comments_2_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Assigned Teachers Comments</t>
+          <t>Assigned Teachers Comments 2 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -998,7 +998,7 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1198,19 +1198,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_teacher_choices</t>
+          <t>assigned_teacher_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>assigned_teacher_choices</t>
+          <t>assigned_teacher_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
